--- a/src/nodes/HPC/compressor_stage_9_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_9_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.000812426092223912</v>
       </c>
       <c r="B2">
-        <v>0.00080206107659377154</v>
+        <v>0.000753965451934116</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.001624852184447824</v>
       </c>
       <c r="B3">
-        <v>0.0011514906313454757</v>
+        <v>0.0010851966622200046</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0024372782766717361</v>
       </c>
       <c r="B4">
-        <v>0.0014343595310308311</v>
+        <v>0.0013540268390317307</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0032497043688956479</v>
       </c>
       <c r="B5">
-        <v>0.0016721214754032445</v>
+        <v>0.0015804798122003871</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.00406213046111956</v>
       </c>
       <c r="B6">
-        <v>0.001873519749939982</v>
+        <v>0.0017727163371862951</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.0048745565533434721</v>
       </c>
       <c r="B7">
-        <v>0.0020435425929189793</v>
+        <v>0.0019353924315221325</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.0056869826455673844</v>
       </c>
       <c r="B8">
-        <v>0.0021851206512120184</v>
+        <v>0.0020712436804239003</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.0064994087377912959</v>
       </c>
       <c r="B9">
-        <v>0.002302839165782338</v>
+        <v>0.0021845499267545364</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.0073118348300152082</v>
       </c>
       <c r="B10">
-        <v>0.0024016492841734765</v>
+        <v>0.0022799325114401412</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.00812426092223912</v>
       </c>
       <c r="B11">
-        <v>0.0024863111861587145</v>
+        <v>0.0023618345100125358</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.0089366870144630319</v>
       </c>
       <c r="B12">
-        <v>0.002559364155111312</v>
+        <v>0.0024326261471074233</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.0097491131066869442</v>
       </c>
       <c r="B13">
-        <v>0.0026146548565747088</v>
+        <v>0.002486564509170318</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.010561539198910857</v>
       </c>
       <c r="B14">
-        <v>0.0026485018882803292</v>
+        <v>0.0025202138046779865</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.011373965291134769</v>
       </c>
       <c r="B15">
-        <v>0.0026758041945413452</v>
+        <v>0.002547479868422394</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.012186391383358679</v>
       </c>
       <c r="B16">
-        <v>0.0027102270151668165</v>
+        <v>0.0025811170648377155</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.012998817475582592</v>
       </c>
       <c r="B17">
-        <v>0.002741920425367595</v>
+        <v>0.0026119322506117692</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.013811243567806504</v>
       </c>
       <c r="B18">
-        <v>0.0027581656938542439</v>
+        <v>0.0026280547128050011</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.014623669660030416</v>
       </c>
       <c r="B19">
-        <v>0.0027582840279343794</v>
+        <v>0.0026288509677147337</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.015436095752254329</v>
       </c>
       <c r="B20">
-        <v>0.0027446066195648787</v>
+        <v>0.0026164968389475068</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.016248521844478239</v>
       </c>
       <c r="B21">
-        <v>0.0027194646607026206</v>
+        <v>0.00259316815010986</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.017060947936702153</v>
       </c>
       <c r="B22">
-        <v>0.0026847744223882763</v>
+        <v>0.0025606534507487629</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.017873374028926064</v>
       </c>
       <c r="B23">
-        <v>0.0026407924919976903</v>
+        <v>0.0025191921941728934</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.018685800121149978</v>
       </c>
       <c r="B24">
-        <v>0.0025873605359904997</v>
+        <v>0.0024686365596313592</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.019498226213373888</v>
       </c>
       <c r="B25">
-        <v>0.0025243202208263421</v>
+        <v>0.0024088387263732666</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.0203106523055978</v>
       </c>
       <c r="B26">
-        <v>0.002451444880824541</v>
+        <v>0.0023395870829701453</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.021123078397821713</v>
       </c>
       <c r="B27">
-        <v>0.002368234521743165</v>
+        <v>0.0022604148552832102</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.021935504490045624</v>
       </c>
       <c r="B28">
-        <v>0.0022741208171999706</v>
+        <v>0.0021707914784961017</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.022747930582269538</v>
       </c>
       <c r="B29">
-        <v>0.0021685354408127141</v>
+        <v>0.0020701863877924565</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.023560356674493448</v>
       </c>
       <c r="B30">
-        <v>0.0020512192659702354</v>
+        <v>0.0019583575906282815</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.024372782766717359</v>
       </c>
       <c r="B31">
-        <v>0.0019231499651457176</v>
+        <v>0.0018362173835490528</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.025185208858941273</v>
       </c>
       <c r="B32">
-        <v>0.0017856144105834252</v>
+        <v>0.0017049666353726126</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.025997634951165183</v>
       </c>
       <c r="B33">
-        <v>0.0016398994745276255</v>
+        <v>0.0015658062149168047</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.026810061043389097</v>
       </c>
       <c r="B34">
-        <v>0.0014867925304396835</v>
+        <v>0.0014194707773136333</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.027622487135613008</v>
       </c>
       <c r="B35">
-        <v>0.0013250829566493578</v>
+        <v>0.0012648301229517477</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.028434913227836919</v>
       </c>
       <c r="B36">
-        <v>0.0011530606327035057</v>
+        <v>0.001100287838533959</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.029247339320060833</v>
       </c>
       <c r="B37">
-        <v>0.00096901543814898242</v>
+        <v>0.000924247510763076</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.030059765412284743</v>
       </c>
       <c r="B38">
-        <v>0.0007700121971454376</v>
+        <v>0.00073396932790120934</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.030872191504508657</v>
       </c>
       <c r="B39">
-        <v>0.000548215512303687</v>
+        <v>0.00052213988444766823</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.031684617596732571</v>
       </c>
       <c r="B40">
-        <v>0.00029456493084733805</v>
+        <v>0.00028030237646106167</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -677,7 +677,7 @@
         <v>0.032497043688956478</v>
       </c>
       <c r="B42">
-        <v>2.8186692293538372E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.031684617596732571</v>
       </c>
       <c r="B43">
-        <v>-0.00013331170074095032</v>
+        <v>-0.00011904914635467396</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.030872191504508657</v>
       </c>
       <c r="B44">
-        <v>-0.0002340533233768719</v>
+        <v>-0.00020797769552085324</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.030059765412284743</v>
       </c>
       <c r="B45">
-        <v>-0.00031127388018141011</v>
+        <v>-0.00027523101093718179</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.029247339320060833</v>
       </c>
       <c r="B46">
-        <v>-0.00037402238342821079</v>
+        <v>-0.00032925445604230436</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.028434913227836919</v>
       </c>
       <c r="B47">
-        <v>-0.00043012319238288943</v>
+        <v>-0.00037735039821334287</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.027622487135613008</v>
       </c>
       <c r="B48">
-        <v>-0.00048250205427893854</v>
+        <v>-0.00042224922058132862</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.026810061043389097</v>
       </c>
       <c r="B49">
-        <v>-0.00053286006334182063</v>
+        <v>-0.00046553831021577038</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.025997634951165183</v>
       </c>
       <c r="B50">
-        <v>-0.0005828983137969976</v>
+        <v>-0.00050880505418617668</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.025185208858941273</v>
       </c>
       <c r="B51">
-        <v>-0.00063381884574094925</v>
+        <v>-0.00055317107053013662</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.024372782766717359</v>
       </c>
       <c r="B52">
-        <v>-0.00068482748275422542</v>
+        <v>-0.00059789490115756076</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.023560356674493448</v>
       </c>
       <c r="B53">
-        <v>-0.00073463099428839359</v>
+        <v>-0.00064176931894643929</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.022747930582269538</v>
       </c>
       <c r="B54">
-        <v>-0.00078193614979502166</v>
+        <v>-0.00068358709677476381</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.021935504490045624</v>
       </c>
       <c r="B55">
-        <v>-0.00082575934391612151</v>
+        <v>-0.00072243000521225189</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.021123078397821713</v>
       </c>
       <c r="B56">
-        <v>-0.00086635547205548321</v>
+        <v>-0.00075853580559552829</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.0203106523055978</v>
       </c>
       <c r="B57">
-        <v>-0.000904289054807341</v>
+        <v>-0.00079243125695294494</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.019498226213373888</v>
       </c>
       <c r="B58">
-        <v>-0.00094012461276592944</v>
+        <v>-0.00082464311831285356</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.018685800121149978</v>
       </c>
       <c r="B59">
-        <v>-0.00097435875478373165</v>
+        <v>-0.00085563477842459049</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.017873374028926064</v>
       </c>
       <c r="B60">
-        <v>-0.0010072164427462253</v>
+        <v>-0.000885616144921428</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.017060947936702153</v>
       </c>
       <c r="B61">
-        <v>-0.0010388547267971369</v>
+        <v>-0.000914733755157623</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.016248521844478239</v>
       </c>
       <c r="B62">
-        <v>-0.0010694306570801925</v>
+        <v>-0.00094313414648743187</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.015436095752254329</v>
       </c>
       <c r="B63">
-        <v>-0.0010986867989562872</v>
+        <v>-0.00097057701833891472</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.014623669660030416</v>
       </c>
       <c r="B64">
-        <v>-0.0011247077786549911</v>
+        <v>-0.00099527471843534527</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.013811243567806504</v>
       </c>
       <c r="B65">
-        <v>-0.0011451637376230432</v>
+        <v>-0.0010150527565738</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.012998817475582592</v>
       </c>
       <c r="B66">
-        <v>-0.0011577248173071822</v>
+        <v>-0.0010277366425513561</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.012186391383358679</v>
       </c>
       <c r="B67">
-        <v>-0.0011630714947062117</v>
+        <v>-0.0010339615443771108</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.011373965291134769</v>
       </c>
       <c r="B68">
-        <v>-0.0011739255890271952</v>
+        <v>-0.0010456012629082437</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.010561539198910857</v>
       </c>
       <c r="B69">
-        <v>-0.0012001406197899454</v>
+        <v>-0.0010718525361876031</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.0097491131066869442</v>
       </c>
       <c r="B70">
-        <v>-0.0012280555655570164</v>
+        <v>-0.0010999652181526254</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.0089366870144630319</v>
       </c>
       <c r="B71">
-        <v>-0.0012427760850053438</v>
+        <v>-0.0011160380770014551</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.00812426092223912</v>
       </c>
       <c r="B72">
-        <v>-0.0012479890982266518</v>
+        <v>-0.0011235124220804727</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.0073118348300152082</v>
       </c>
       <c r="B73">
-        <v>-0.0012498538978265885</v>
+        <v>-0.0011281371250932528</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.0064994087377912959</v>
       </c>
       <c r="B74">
-        <v>-0.00124583800505171</v>
+        <v>-0.0011275487660239081</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.0056869826455673844</v>
       </c>
       <c r="B75">
-        <v>-0.0012311884724315238</v>
+        <v>-0.0011173115016434058</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.0048745565533434721</v>
       </c>
       <c r="B76">
-        <v>-0.0012009622489864351</v>
+        <v>-0.0010928120875895878</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.00406213046111956</v>
       </c>
       <c r="B77">
-        <v>-0.0011505826326706232</v>
+        <v>-0.0010497792199169363</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0032497043688956479</v>
       </c>
       <c r="B78">
-        <v>-0.0010771284206824729</v>
+        <v>-0.00098548675747961553</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0024372782766717361</v>
       </c>
       <c r="B79">
-        <v>-0.00097562122894218127</v>
+        <v>-0.00089528853694308087</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.001624852184447824</v>
       </c>
       <c r="B80">
-        <v>-0.00083732844241866011</v>
+        <v>-0.00077103447329318891</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.000812426092223912</v>
       </c>
       <c r="B81">
-        <v>-0.000640807663195896</v>
+        <v>-0.0005927120385362404</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.00093980482913179082</v>
       </c>
       <c r="B2">
-        <v>0.00040380742701436138</v>
+        <v>0.000307834557863423</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0018796096582635816</v>
       </c>
       <c r="B3">
-        <v>0.00058857440094751187</v>
+        <v>0.00045628747319892106</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0028194144873953729</v>
       </c>
       <c r="B4">
-        <v>0.00074038377659262089</v>
+        <v>0.00058008314649726962</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0037592193165271633</v>
       </c>
       <c r="B5">
-        <v>0.00086957482349467818</v>
+        <v>0.00068670759984221425</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0046990241456589541</v>
       </c>
       <c r="B6">
-        <v>0.00098036052940599517</v>
+        <v>0.00077921140595375578</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0056388289747907458</v>
       </c>
       <c r="B7">
-        <v>0.001075144064221609</v>
+        <v>0.00085933480169841784</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0065786338039225366</v>
       </c>
       <c r="B8">
-        <v>0.0011553368971562814</v>
+        <v>0.000928100018664899</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0075184386330543265</v>
       </c>
       <c r="B9">
-        <v>0.0012231481095831551</v>
+        <v>0.00098710672869841451</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0084582434621861182</v>
       </c>
       <c r="B10">
-        <v>0.0012809631996551205</v>
+        <v>0.0010380823142175349</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.0093980482913179082</v>
       </c>
       <c r="B11">
-        <v>0.0013310757204856804</v>
+        <v>0.0010826875596777379</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.0103378531204497</v>
       </c>
       <c r="B12">
-        <v>0.0013747088137375078</v>
+        <v>0.0011218082568847569</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.011277657949581492</v>
       </c>
       <c r="B13">
-        <v>0.001408895920309344</v>
+        <v>0.001153296825008439</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.012217462778713282</v>
       </c>
       <c r="B14">
-        <v>0.0014318619909281963</v>
+        <v>0.0011758683210607542</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.013157267607845073</v>
       </c>
       <c r="B15">
-        <v>0.001450787716398067</v>
+        <v>0.0011947217260580496</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.014097072436976863</v>
       </c>
       <c r="B16">
-        <v>0.0014722591922769518</v>
+        <v>0.0012146255206757794</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.015036877266108653</v>
       </c>
       <c r="B17">
-        <v>0.0014915283930618255</v>
+        <v>0.0012321422602214513</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.015976682095240446</v>
       </c>
       <c r="B18">
-        <v>0.0015024646007467187</v>
+        <v>0.001242833412926553</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.016916486924372236</v>
       </c>
       <c r="B19">
-        <v>0.0015047404483749095</v>
+        <v>0.0012464620240864382</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.017856291753504026</v>
       </c>
       <c r="B20">
-        <v>0.0014994794067519886</v>
+        <v>0.0012438415332624263</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.018796096582635816</v>
       </c>
       <c r="B21">
-        <v>0.0014878049466835455</v>
+        <v>0.0012357853800158377</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.019735901411767606</v>
       </c>
       <c r="B22">
-        <v>0.0014706405989136759</v>
+        <v>0.0012229622320280734</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.0206757062408994</v>
       </c>
       <c r="B23">
-        <v>0.0014481101339404987</v>
+        <v>0.0012054616694608614</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.02161551107003119</v>
       </c>
       <c r="B24">
-        <v>0.0014201373822006378</v>
+        <v>0.0011832285005960099</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.022555315899162983</v>
       </c>
       <c r="B25">
-        <v>0.0013866461741307173</v>
+        <v>0.0011562075337153289</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.02349512072829477</v>
       </c>
       <c r="B26">
-        <v>0.0013475274524817535</v>
+        <v>0.0011243197517197907</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.024434925557426563</v>
       </c>
       <c r="B27">
-        <v>0.0013025406092623281</v>
+        <v>0.0010873908359870228</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.025374730386558353</v>
       </c>
       <c r="B28">
-        <v>0.0012514121487954156</v>
+        <v>0.0010452226425138164</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.026314535215690146</v>
       </c>
       <c r="B29">
-        <v>0.00119386857540399</v>
+        <v>0.00099761702729696277</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.027254340044821936</v>
       </c>
       <c r="B30">
-        <v>0.0011297854751083018</v>
+        <v>0.00094448376669310362</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.028194144873953726</v>
       </c>
       <c r="B31">
-        <v>0.0010596347607177092</v>
+        <v>0.000886164318498283</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.029133949703085516</v>
       </c>
       <c r="B32">
-        <v>0.00098403742673884576</v>
+        <v>0.00082310806086839455</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.030073754532217306</v>
       </c>
       <c r="B33">
-        <v>0.00090361446767834609</v>
+        <v>0.00075576437195933272</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.0310135593613491</v>
       </c>
       <c r="B34">
-        <v>0.00081874617384529891</v>
+        <v>0.00068440834479121507</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.031953364190480893</v>
       </c>
       <c r="B35">
-        <v>0.00072885001875861062</v>
+        <v>0.00060861793184105234</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.032893169019612679</v>
       </c>
       <c r="B36">
-        <v>0.00063310277173964254</v>
+        <v>0.00052779680045007935</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.033832973848744473</v>
       </c>
       <c r="B37">
-        <v>0.00053068120210975447</v>
+        <v>0.00044134861795952962</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.034772778677876259</v>
       </c>
       <c r="B38">
-        <v>0.00042017165600424187</v>
+        <v>0.00034824957165085243</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.035712583507008053</v>
       </c>
       <c r="B39">
-        <v>0.00029779878681413527</v>
+        <v>0.0002457659285663563</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.036652388336139846</v>
       </c>
       <c r="B40">
-        <v>0.00015919682474439952</v>
+        <v>0.00013073647568856423</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.037592193165271633</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>3.2606029998625788E-20</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.036652388336139846</v>
       </c>
       <c r="B43">
-        <v>-4.7037588703682283E-05</v>
+        <v>-1.8577239647846989E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.035712583507008053</v>
       </c>
       <c r="B44">
-        <v>-7.9250910633538521E-05</v>
+        <v>-2.7218052385759548E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.034772778677876259</v>
       </c>
       <c r="B45">
-        <v>-0.00010100286829568118</v>
+        <v>-2.9080783942291839E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.033832973848744473</v>
       </c>
       <c r="B46">
-        <v>-0.00011665636419622301</v>
+        <v>-2.7323780045998151E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.032893169019612679</v>
       </c>
       <c r="B47">
-        <v>-0.00012998397673545263</v>
+        <v>-2.4678005445889531E-05</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.031953364190480893</v>
       </c>
       <c r="B48">
-        <v>-0.00014239698789036235</v>
+        <v>-2.2164900972804091E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.0310135593613491</v>
       </c>
       <c r="B49">
-        <v>-0.00015471635553212059</v>
+        <v>-2.0378526478036687E-05</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.030073754532217306</v>
       </c>
       <c r="B50">
-        <v>-0.00016776303753189556</v>
+        <v>-1.9912941812882208E-05</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.029133949703085516</v>
       </c>
       <c r="B51">
-        <v>-0.00018211739840935103</v>
+        <v>-2.1188032538899863E-05</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.028194144873953726</v>
       </c>
       <c r="B52">
-        <v>-0.00019739742927813231</v>
+        <v>-2.3926987058706228E-05</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.027254340044821936</v>
       </c>
       <c r="B53">
-        <v>-0.00021298052790038027</v>
+        <v>-2.7678819485182189E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.026314535215690146</v>
       </c>
       <c r="B54">
-        <v>-0.00022824409203823579</v>
+        <v>-3.1992543931208696E-05</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.025374730386558353</v>
       </c>
       <c r="B55">
-        <v>-0.00024271470831762243</v>
+        <v>-3.6525202036023226E-05</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.024434925557426563</v>
       </c>
       <c r="B56">
-        <v>-0.000256515718819595</v>
+        <v>-4.1365945544289636E-05</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.02349512072829477</v>
       </c>
       <c r="B57">
-        <v>-0.00026991965448899114</v>
+        <v>-4.6711953727028376E-05</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.022555315899162983</v>
       </c>
       <c r="B58">
-        <v>-0.00028319904627064832</v>
+        <v>-5.2760405855259864E-05</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.02161551107003119</v>
       </c>
       <c r="B59">
-        <v>-0.00029659364391985293</v>
+        <v>-5.9684762315225227E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.0206757062408994</v>
       </c>
       <c r="B60">
-        <v>-0.00031021207243368544</v>
+        <v>-6.7563607954048029E-05</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.019735901411767606</v>
       </c>
       <c r="B61">
-        <v>-0.00032413017561967489</v>
+        <v>-7.6451808734072512E-05</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.018796096582635816</v>
       </c>
       <c r="B62">
-        <v>-0.00033842379728535045</v>
+        <v>-8.6404230617642883E-05</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.017856291753504026</v>
       </c>
       <c r="B63">
-        <v>-0.00035296895186802651</v>
+        <v>-9.7331078378464533E-05</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.016916486924372236</v>
       </c>
       <c r="B64">
-        <v>-0.00036684233632415888</v>
+        <v>-0.0001085639120356875</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.015976682095240446</v>
       </c>
       <c r="B65">
-        <v>-0.0003789208182399885</v>
+        <v>-0.00011928963041982292</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.015036877266108653</v>
       </c>
       <c r="B66">
-        <v>-0.00038808126520175631</v>
+        <v>-0.00012869513236138201</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.014097072436976863</v>
       </c>
       <c r="B67">
-        <v>-0.00039465147149966216</v>
+        <v>-0.00013701779989848945</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.013157267607845073</v>
       </c>
       <c r="B68">
-        <v>-0.00040476293823974124</v>
+        <v>-0.00014869694789972372</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.012217462778713282</v>
       </c>
       <c r="B69">
-        <v>-0.00042316460231413684</v>
+        <v>-0.0001671709324466949</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.011277657949581492</v>
       </c>
       <c r="B70">
-        <v>-0.00044327143694358951</v>
+        <v>-0.00018767234164268468</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.0103378531204497</v>
       </c>
       <c r="B71">
-        <v>-0.00045790391707952664</v>
+        <v>-0.00020500336022677583</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.0093980482913179082</v>
       </c>
       <c r="B72">
-        <v>-0.00046883848826752538</v>
+        <v>-0.00022045032745958301</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0084582434621861182</v>
       </c>
       <c r="B73">
-        <v>-0.00047904321655926793</v>
+        <v>-0.00023616233112168234</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0075184386330543265</v>
       </c>
       <c r="B74">
-        <v>-0.00048729667943670445</v>
+        <v>-0.00025125529855196389</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0065786338039225366</v>
       </c>
       <c r="B75">
-        <v>-0.00049130714988272262</v>
+        <v>-0.00026407027139134016</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0056388289747907458</v>
       </c>
       <c r="B76">
-        <v>-0.00048869117145369085</v>
+        <v>-0.00027288190893049954</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0046990241456589541</v>
       </c>
       <c r="B77">
-        <v>-0.00047724181445081191</v>
+        <v>-0.00027609269099857251</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0037592193165271633</v>
       </c>
       <c r="B78">
-        <v>-0.00045554998558114672</v>
+        <v>-0.00027268276192868286</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0028194144873953729</v>
       </c>
       <c r="B79">
-        <v>-0.00042121499221427265</v>
+        <v>-0.00026091436211892139</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0018796096582635816</v>
       </c>
       <c r="B80">
-        <v>-0.00037002652476691463</v>
+        <v>-0.00023773959701832383</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00093980482913179082</v>
       </c>
       <c r="B81">
-        <v>-0.00029164814654316376</v>
+        <v>-0.00019567527739222535</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0010561539198910856</v>
       </c>
       <c r="B2">
-        <v>0.0002777002639230622</v>
+        <v>0.00019954487385112187</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0021123078397821712</v>
       </c>
       <c r="B3">
-        <v>0.00040743071995552366</v>
+        <v>0.00029970302012663296</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0031684617596732575</v>
       </c>
       <c r="B4">
-        <v>0.00051466299673302049</v>
+        <v>0.00038412237223448231</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0042246156795643424</v>
       </c>
       <c r="B5">
-        <v>0.00060636822352720817</v>
+        <v>0.00045745052082256507</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0052807695994554283</v>
       </c>
       <c r="B6">
-        <v>0.00068538671973318219</v>
+        <v>0.000521581174008441</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.006336923519346515</v>
       </c>
       <c r="B7">
-        <v>0.00075333851083807636</v>
+        <v>0.00057759449856819981</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0073930774392376</v>
       </c>
       <c r="B8">
-        <v>0.00081117495348122823</v>
+        <v>0.00062612487595053621</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0084492313591286849</v>
       </c>
       <c r="B9">
-        <v>0.00086038525397308266</v>
+        <v>0.00066816524055290482</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.00950538527901977</v>
       </c>
       <c r="B10">
-        <v>0.000902577590266324</v>
+        <v>0.00070478783457465354</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.010561539198910857</v>
       </c>
       <c r="B11">
-        <v>0.00093929817721148787</v>
+        <v>0.00073702357847394708</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.011617693118801942</v>
       </c>
       <c r="B12">
-        <v>0.00097137148845860457</v>
+        <v>0.00076542222545228562</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.01267384703869303</v>
       </c>
       <c r="B13">
-        <v>0.00099679699595783323</v>
+        <v>0.000788650181425698</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.013730000958584114</v>
       </c>
       <c r="B14">
-        <v>0.001014377601098537</v>
+        <v>0.00080590946524473016</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.0147861548784752</v>
       </c>
       <c r="B15">
-        <v>0.0010289549247267655</v>
+        <v>0.00082042789478346942</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.015842308798366286</v>
       </c>
       <c r="B16">
-        <v>0.0010449696786189267</v>
+        <v>0.00083516600933413745</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.01689846271825737</v>
       </c>
       <c r="B17">
-        <v>0.00105922021881617</v>
+        <v>0.00084798943483795281</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.017954616638148457</v>
       </c>
       <c r="B18">
-        <v>0.0010675725982853485</v>
+        <v>0.00085614225408032877</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.019010770558039541</v>
       </c>
       <c r="B19">
-        <v>0.0010698060134313821</v>
+        <v>0.00085947729057445782</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.020066924477930629</v>
       </c>
       <c r="B20">
-        <v>0.0010666779465187074</v>
+        <v>0.00085849955301547768</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.021123078397821713</v>
       </c>
       <c r="B21">
-        <v>0.0010589458798117616</v>
+        <v>0.0008537140500985258</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.0221792323177128</v>
       </c>
       <c r="B22">
-        <v>0.0010472324970126415</v>
+        <v>0.00084553591809843139</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.023235386237603885</v>
       </c>
       <c r="B23">
-        <v>0.0010316212875740856</v>
+        <v>0.00083402080360879</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.024291540157494972</v>
       </c>
       <c r="B24">
-        <v>0.001012060942386493</v>
+        <v>0.00081913448080288861</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.02534769407738606</v>
       </c>
       <c r="B25">
-        <v>0.0009885001523402626</v>
+        <v>0.00080084272385401456</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.02640384799727714</v>
       </c>
       <c r="B26">
-        <v>0.00096086544933295386</v>
+        <v>0.00077909652781956015</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.027460001917168228</v>
       </c>
       <c r="B27">
-        <v>0.00092899472929076519</v>
+        <v>0.00075378777129333845</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.028516155837059316</v>
       </c>
       <c r="B28">
-        <v>0.00089270372914705589</v>
+        <v>0.00072479355375326758</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.0295723097569504</v>
       </c>
       <c r="B29">
-        <v>0.00085180818583518482</v>
+        <v>0.00069199097467726573</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.030628463676841487</v>
       </c>
       <c r="B30">
-        <v>0.00080622437589385535</v>
+        <v>0.00065532415346317965</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.031684617596732571</v>
       </c>
       <c r="B31">
-        <v>0.00075627073428314847</v>
+        <v>0.00061500528918856823</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.032740771516623655</v>
       </c>
       <c r="B32">
-        <v>0.0007023662355684886</v>
+        <v>0.00057131360085091844</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.03379692543651474</v>
       </c>
       <c r="B33">
-        <v>0.000644929854315301</v>
+        <v>0.00052452830744771726</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.034853079356405831</v>
       </c>
       <c r="B34">
-        <v>0.0005842182801857888</v>
+        <v>0.00047482043135595723</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.035909233276296915</v>
       </c>
       <c r="B35">
-        <v>0.00051983906322926744</v>
+        <v>0.00042192820847065135</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.036965387196188</v>
       </c>
       <c r="B36">
-        <v>0.00045123746859183109</v>
+        <v>0.0003654816780663179</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.038021541116079083</v>
       </c>
       <c r="B37">
-        <v>0.000377858761419573</v>
+        <v>0.00030511087941747497</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.039077695035970174</v>
       </c>
       <c r="B38">
-        <v>0.000298750111385084</v>
+        <v>0.00024018044886321306</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.040133848955861258</v>
       </c>
       <c r="B39">
-        <v>0.0002113663062669422</v>
+        <v>0.00016899341100091189</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.041190002875752342</v>
       </c>
       <c r="B40">
-        <v>0.00011276403837022238</v>
+        <v>8.9587387492523441E-05</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.042246156795643426</v>
       </c>
       <c r="B42">
-        <v>-9.1606749953999718E-21</v>
+        <v>4.294066404093737E-22</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.041190002875752342</v>
       </c>
       <c r="B43">
-        <v>-2.629586689597134E-05</v>
+        <v>-3.1192160182723685E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.040133848955861258</v>
       </c>
       <c r="B44">
-        <v>-4.2871065329239458E-05</v>
+        <v>-4.9817006320915709E-07</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.039077695035970174</v>
       </c>
       <c r="B45">
-        <v>-5.2667863746141528E-05</v>
+        <v>5.90179877572942E-06</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.038021541116079083</v>
       </c>
       <c r="B46">
-        <v>-5.862853059301488E-05</v>
+        <v>1.4119351409083115E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.036965387196188</v>
       </c>
       <c r="B47">
-        <v>-6.3297274561247382E-05</v>
+        <v>2.2458515964265719E-05</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.035909233276296915</v>
       </c>
       <c r="B48">
-        <v>-6.7626065322428977E-05</v>
+        <v>3.0284789436187112E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.034853079356405831</v>
       </c>
       <c r="B49">
-        <v>-7.2168812793200207E-05</v>
+        <v>3.7229036036631319E-05</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.03379692543651474</v>
       </c>
       <c r="B50">
-        <v>-7.7479426890201568E-05</v>
+        <v>4.2922119977382243E-05</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.032740771516623655</v>
       </c>
       <c r="B51">
-        <v>-8.39495727369331E-05</v>
+        <v>4.7103061980637236E-05</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.031684617596732571</v>
       </c>
       <c r="B52">
-        <v>-9.1321936284333052E-05</v>
+        <v>4.9943508810247244E-05</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.030628463676841487</v>
       </c>
       <c r="B53">
-        <v>-9.9176958690199208E-05</v>
+        <v>5.1723263740476587E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.0295723097569504</v>
       </c>
       <c r="B54">
-        <v>-0.00010709508111232944</v>
+        <v>5.2722130045589641E-05</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.028516155837059316</v>
       </c>
       <c r="B55">
-        <v>-0.00011475732321567429</v>
+        <v>5.3152852178114115E-05</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.027460001917168228</v>
       </c>
       <c r="B56">
-        <v>-0.00012224701869379556</v>
+        <v>5.2959939303631294E-05</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.02640384799727714</v>
       </c>
       <c r="B57">
-        <v>-0.00012974807974740782</v>
+        <v>5.2020841765985881E-05</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.02534769407738606</v>
       </c>
       <c r="B58">
-        <v>-0.00013744441857722558</v>
+        <v>5.0213009909022545E-05</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.024291540157494972</v>
       </c>
       <c r="B59">
-        <v>-0.00014549782711513243</v>
+        <v>4.7428634468471895E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.023235386237603885</v>
       </c>
       <c r="B60">
-        <v>-0.00015398161621768731</v>
+        <v>4.3618867747608247E-05</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.0221792323177128</v>
       </c>
       <c r="B61">
-        <v>-0.00016294697647261815</v>
+        <v>3.8749602441591863E-05</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.021123078397821713</v>
       </c>
       <c r="B62">
-        <v>-0.00017244509846765281</v>
+        <v>3.2786731245583E-05</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.020066924477930629</v>
       </c>
       <c r="B63">
-        <v>-0.00018239241450067147</v>
+        <v>2.5785979002558439E-05</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.019010770558039541</v>
       </c>
       <c r="B64">
-        <v>-0.00019216632371016337</v>
+        <v>1.8162399146760938E-05</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.017954616638148457</v>
       </c>
       <c r="B65">
-        <v>-0.00020100946694476997</v>
+        <v>1.0420877260249849E-05</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.01689846271825737</v>
       </c>
       <c r="B66">
-        <v>-0.00020816448505313272</v>
+        <v>3.0662989250844437E-06</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.015842308798366286</v>
       </c>
       <c r="B67">
-        <v>-0.00021385233708980781</v>
+        <v>-4.0486678050187362E-06</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.0147861548784752</v>
       </c>
       <c r="B68">
-        <v>-0.00022220725493301026</v>
+        <v>-1.3680224989714265E-05</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.013730000958584114</v>
       </c>
       <c r="B69">
-        <v>-0.00023643121402430249</v>
+        <v>-2.7963078170495887E-05</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.01267384703869303</v>
       </c>
       <c r="B70">
-        <v>-0.00025208389123497764</v>
+        <v>-4.3937076702842445E-05</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.011617693118801942</v>
       </c>
       <c r="B71">
-        <v>-0.00026432408957930868</v>
+        <v>-5.8374826572989769E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.010561539198910857</v>
       </c>
       <c r="B72">
-        <v>-0.0002743494152137564</v>
+        <v>-7.2074816476215632E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.00950538527901977</v>
       </c>
       <c r="B73">
-        <v>-0.00028416094388369732</v>
+        <v>-8.6371188192027029E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0084492313591286849</v>
       </c>
       <c r="B74">
-        <v>-0.00029293482654798306</v>
+        <v>-0.00010071481312780538</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0073930774392376</v>
       </c>
       <c r="B75">
-        <v>-0.00029912551170292311</v>
+        <v>-0.00011407543417223113</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.006336923519346515</v>
       </c>
       <c r="B76">
-        <v>-0.00030112556278118343</v>
+        <v>-0.00012538155051130666</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0052807695994554283</v>
       </c>
       <c r="B77">
-        <v>-0.00029744655461526461</v>
+        <v>-0.0001336410088905234</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0042246156795643424</v>
       </c>
       <c r="B78">
-        <v>-0.00028713799270065012</v>
+        <v>-0.00013822028999600699</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0031684617596732575</v>
       </c>
       <c r="B79">
-        <v>-0.00026858075025820857</v>
+        <v>-0.00013804012575967036</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0021123078397821712</v>
       </c>
       <c r="B80">
-        <v>-0.00023893547901782057</v>
+        <v>-0.00013120777918892987</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0010561539198910856</v>
       </c>
       <c r="B81">
-        <v>-0.00019123207650857977</v>
+        <v>-0.00011307668643663942</v>
       </c>
     </row>
     <row r="82" spans="1:2">
